--- a/06_Testing_Results_and_Evaluation/Requirements_Traceability_Matrix.xlsx
+++ b/06_Testing_Results_and_Evaluation/Requirements_Traceability_Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gedion\Desktop\TrackWIL\06_Testing_Results_and_Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FDBC9E-7FC5-4865-B2F8-6883C6DC9FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69ED8EC-4D2B-4315-826C-FA8E35B6D841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$I$103</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tracker!$A$3:$I$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tracker!$A$1:$I$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Tracker!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
   <si>
     <t>REQUIREMENTS TRACEABILITY MATRIX</t>
   </si>
@@ -108,15 +108,6 @@
     <t>Restrict each page and action to the roles allowed to use it.</t>
   </si>
   <si>
-    <t>Access control layer (proxy, layouts, session)</t>
-  </si>
-  <si>
-    <t>src/proxy.ts; src/app/student/layout.tsx; src/app/coordinator/layout.tsx; ownership checks in actions</t>
-  </si>
-  <si>
-    <t>TC-112, TC-117, TC-118, TC-119, TC-120, TC-120b, TC-121</t>
-  </si>
-  <si>
     <t>FR-04</t>
   </si>
   <si>
@@ -210,33 +201,15 @@
     <t>FR-10</t>
   </si>
   <si>
-    <t>Student views all entries, newest first, and verified hours against required hours.</t>
-  </si>
-  <si>
     <t>Student logbook page</t>
   </si>
   <si>
-    <t>src/app/student/page.tsx; sumVerifiedHours</t>
-  </si>
-  <si>
-    <t>TC-002, TC-006, TC-132, TC-138</t>
-  </si>
-  <si>
     <t>FR-11</t>
   </si>
   <si>
-    <t>Coordinators and lecturers see each student's status, verified hours, entries and pending count.</t>
-  </si>
-  <si>
     <t>UC-06; coordinator dashboard</t>
   </si>
   <si>
-    <t>src/app/coordinator/page.tsx; studentOverviewStatus</t>
-  </si>
-  <si>
-    <t>TC-009, TC-139</t>
-  </si>
-  <si>
     <t>FR-12</t>
   </si>
   <si>
@@ -333,9 +306,6 @@
     <t>src/lib/password.ts; src/lib/session.ts; src/app/actions/logbook.ts (randomBytes(24))</t>
   </si>
   <si>
-    <t>TC-121, TC-126, TC-127, TC-142</t>
-  </si>
-  <si>
     <t>NFR-04</t>
   </si>
   <si>
@@ -390,10 +360,100 @@
     <t>Data minimisation; Ethical Clearance</t>
   </si>
   <si>
-    <t>database/seed.sql</t>
-  </si>
-  <si>
     <t>TC-148</t>
+  </si>
+  <si>
+    <t>Access control layer (proxy, layouts, page-level role checks, session)</t>
+  </si>
+  <si>
+    <t>src/proxy.ts; src/lib/session.ts (requireRole on every protected page and layout); ownership checks in actions</t>
+  </si>
+  <si>
+    <t>TC-112, TC-117, TC-118, TC-119, TC-120, TC-120b, TC-121, TC-154, TC-168, TC-171</t>
+  </si>
+  <si>
+    <t>Student views each placement's entries, newest first, and its verified hours against its required hours.</t>
+  </si>
+  <si>
+    <t>src/app/student/page.tsx; src/app/student/placements/[id]/page.tsx; sumVerifiedHours</t>
+  </si>
+  <si>
+    <t>TC-002, TC-006, TC-132, TC-138, TC-155</t>
+  </si>
+  <si>
+    <t>Coordinators and lecturers see each student's status for their current placement, verified hours, entries, pending count and missing documents.</t>
+  </si>
+  <si>
+    <t>src/app/coordinator/page.tsx; studentOverviewStatus, currentPlacement</t>
+  </si>
+  <si>
+    <t>TC-009, TC-139, TC-170, TC-174</t>
+  </si>
+  <si>
+    <t>FR-15</t>
+  </si>
+  <si>
+    <t>Add WIL placements, each with its own required hours; every entry belongs to a placement.</t>
+  </si>
+  <si>
+    <t>UC-08; wil_placements table; placement pages</t>
+  </si>
+  <si>
+    <t>src/app/actions/placements.ts; src/app/student/placements; src/lib/repository.ts</t>
+  </si>
+  <si>
+    <t>TC-150, TC-151, TC-152, TC-153, TC-154, TC-155, TC-156, TC-174</t>
+  </si>
+  <si>
+    <t>FR-16</t>
+  </si>
+  <si>
+    <t>Upload WIL documents: MOU, Commencement Letter and Code of Conduct per placement; Attendance Register per semester.</t>
+  </si>
+  <si>
+    <t>UC-09; placement_documents table; documents section</t>
+  </si>
+  <si>
+    <t>src/app/actions/documents.ts; src/lib/documents.ts; src/app/api/documents/[id]/route.ts</t>
+  </si>
+  <si>
+    <t>TC-157, TC-158, TC-159, TC-160, TC-161, TC-162, TC-163, TC-164, TC-165</t>
+  </si>
+  <si>
+    <t>FR-17</t>
+  </si>
+  <si>
+    <t>Coordinators and lecturers open a student's profile with placements, documents and logbook.</t>
+  </si>
+  <si>
+    <t>UC-10; student profile page</t>
+  </si>
+  <si>
+    <t>src/app/coordinator/students/[id]/page.tsx</t>
+  </si>
+  <si>
+    <t>TC-166, TC-167, TC-168, TC-169, TC-170</t>
+  </si>
+  <si>
+    <t>FR-18</t>
+  </si>
+  <si>
+    <t>A placement is WIL completed when its verified hours reach its required hours, and is then locked.</t>
+  </si>
+  <si>
+    <t>Status rules; locks in the Server Actions</t>
+  </si>
+  <si>
+    <t>src/lib/logbook-metrics.ts (placementCompletion, studentOverviewStatus); checks in src/app/actions</t>
+  </si>
+  <si>
+    <t>TC-172, TC-173, TC-174</t>
+  </si>
+  <si>
+    <t>TC-121, TC-126, TC-127, TC-142, TC-160, TC-162, TC-171</t>
+  </si>
+  <si>
+    <t>database/seed.sql; database/demo-documents</t>
   </si>
 </sst>
 </file>
@@ -810,7 +870,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -922,7 +982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -936,13 +996,13 @@
         <v>13</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
@@ -953,10 +1013,10 @@
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
@@ -965,13 +1025,13 @@
         <v>13</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>17</v>
@@ -982,10 +1042,10 @@
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>12</v>
@@ -994,13 +1054,13 @@
         <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>17</v>
@@ -1011,10 +1071,10 @@
     </row>
     <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>12</v>
@@ -1023,13 +1083,13 @@
         <v>13</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>17</v>
@@ -1040,10 +1100,10 @@
     </row>
     <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
@@ -1052,13 +1112,13 @@
         <v>13</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>17</v>
@@ -1069,10 +1129,10 @@
     </row>
     <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>12</v>
@@ -1081,13 +1141,13 @@
         <v>13</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>17</v>
@@ -1098,10 +1158,10 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>12</v>
@@ -1110,13 +1170,13 @@
         <v>13</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>17</v>
@@ -1127,10 +1187,10 @@
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>12</v>
@@ -1139,13 +1199,13 @@
         <v>13</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>17</v>
@@ -1154,12 +1214,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>12</v>
@@ -1168,13 +1228,13 @@
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>17</v>
@@ -1185,10 +1245,10 @@
     </row>
     <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>12</v>
@@ -1197,13 +1257,13 @@
         <v>21</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>17</v>
@@ -1214,10 +1274,10 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>12</v>
@@ -1226,13 +1286,13 @@
         <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>17</v>
@@ -1243,10 +1303,10 @@
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>12</v>
@@ -1255,13 +1315,13 @@
         <v>13</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>17</v>
@@ -1270,56 +1330,56 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>17</v>
@@ -1328,27 +1388,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>17</v>
@@ -1357,27 +1417,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>17</v>
@@ -1386,56 +1446,56 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>17</v>
@@ -1444,27 +1504,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>17</v>
@@ -1473,49 +1533,121 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -1682,22 +1814,66 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I103" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:I107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C4:C43" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C4:C47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Functional,Non-Functional"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D43" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D4:D47" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Must,Should,Could"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H4:H43" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H4:H47" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Pass,Fail,Not Tested"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I4:I43" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I4:I47" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Met,Partially Met,Not Met"</formula1>
     </dataValidation>
   </dataValidations>
